--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5880301F-56C2-3A49-8CE7-516D7DD90714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B13B7A4-45C1-214B-BACD-CB50AC4A9B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -14447,7 +14447,7 @@
         <v>698</v>
       </c>
       <c r="T198" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.2">
@@ -14502,7 +14502,7 @@
         <v>698</v>
       </c>
       <c r="T199" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B13B7A4-45C1-214B-BACD-CB50AC4A9B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA38ED3-0D0B-BE42-B9B2-CBE2869BB876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5611" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="1053">
   <si>
     <t>State</t>
   </si>
@@ -3223,6 +3223,15 @@
   </si>
   <si>
     <t>Macallister, Tyler</t>
+  </si>
+  <si>
+    <t>DiLorenzo, Anthony</t>
+  </si>
+  <si>
+    <t>Williams, Lily Tang</t>
+  </si>
+  <si>
+    <t>Shaheen, Stefany</t>
   </si>
 </sst>
 </file>
@@ -3762,8 +3771,8 @@
         <v>-30.199999999999996</v>
       </c>
       <c r="G2" s="3">
-        <f>E2+6.8+1.5</f>
-        <v>-27.999999999999996</v>
+        <f>E2+6.5+1.5</f>
+        <v>-28.299999999999997</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>963</v>
@@ -3806,8 +3815,8 @@
         <v>-11.799999999999997</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G66" si="0">E3+6.8+1.5</f>
-        <v>-9.0000000000000036</v>
+        <f t="shared" ref="G3:G66" si="0">E3+6.5+1.5</f>
+        <v>-9.3000000000000043</v>
       </c>
       <c r="H3" t="s">
         <v>964</v>
@@ -3851,7 +3860,7 @@
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>-37.600000000000009</v>
+        <v>-37.900000000000006</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>11</v>
@@ -3895,7 +3904,7 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>-59.500000000000014</v>
+        <v>-59.800000000000011</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
@@ -3939,7 +3948,7 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>-20.7</v>
+        <v>-21</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>994</v>
@@ -3983,7 +3992,7 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>-26.699999999999992</v>
+        <v>-26.999999999999993</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>984</v>
@@ -4027,7 +4036,7 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>33.099999999999994</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -4070,7 +4079,7 @@
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>-4.8</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
@@ -4122,7 +4131,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>5.1999999999999993</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>894</v>
@@ -4177,7 +4186,7 @@
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>-6.6000000000000014</v>
+        <v>-6.9</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>811</v>
@@ -4232,7 +4241,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
       <c r="H12" t="s">
         <v>21</v>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -4342,7 +4351,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
-        <v>-11.599999999999998</v>
+        <v>-11.899999999999999</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>882</v>
@@ -4397,7 +4406,7 @@
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>813</v>
@@ -4452,7 +4461,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
-        <v>30.400000000000002</v>
+        <v>30.1</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
@@ -4507,7 +4516,7 @@
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
-        <v>-8</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>883</v>
@@ -4562,7 +4571,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
-        <v>-22.7</v>
+        <v>-23</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>816</v>
@@ -4617,7 +4626,7 @@
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
-        <v>-37</v>
+        <v>-37.299999999999997</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>29</v>
@@ -4672,7 +4681,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
-        <v>-7.3000000000000007</v>
+        <v>-7.6</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>31</v>
@@ -4727,7 +4736,7 @@
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
-        <v>-16.599999999999998</v>
+        <v>-16.899999999999999</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>33</v>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
-        <v>-31.6</v>
+        <v>-31.9</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>35</v>
@@ -4837,7 +4846,7 @@
       </c>
       <c r="G23" s="3">
         <f t="shared" si="0"/>
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>739</v>
@@ -4893,7 +4902,7 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" si="0"/>
-        <v>32.900000000000006</v>
+        <v>32.6</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>37</v>
@@ -4948,7 +4957,7 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>741</v>
@@ -5004,7 +5013,7 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" si="0"/>
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>38</v>
@@ -5059,7 +5068,7 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
-        <v>-12.3</v>
+        <v>-12.600000000000001</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>743</v>
@@ -5114,7 +5123,7 @@
       </c>
       <c r="G28" s="3">
         <f t="shared" si="0"/>
-        <v>16.600000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>790</v>
@@ -5169,7 +5178,7 @@
       </c>
       <c r="G29" s="3">
         <f t="shared" si="0"/>
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="H29" t="s">
         <v>40</v>
@@ -5224,7 +5233,7 @@
       </c>
       <c r="G30" s="3">
         <f t="shared" si="0"/>
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
         <v>41</v>
@@ -5279,7 +5288,7 @@
       </c>
       <c r="G31" s="3">
         <f t="shared" si="0"/>
-        <v>19.7</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
@@ -5335,7 +5344,7 @@
       </c>
       <c r="G32" s="3">
         <f t="shared" si="0"/>
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="H32" t="s">
         <v>43</v>
@@ -5390,7 +5399,7 @@
       </c>
       <c r="G33" s="3">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>75.7</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>736</v>
@@ -5445,7 +5454,7 @@
       </c>
       <c r="G34" s="3">
         <f t="shared" si="0"/>
-        <v>82.1</v>
+        <v>81.8</v>
       </c>
       <c r="H34" t="s">
         <v>45</v>
@@ -5500,7 +5509,7 @@
       </c>
       <c r="G35" s="3">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
+        <v>8.4</v>
       </c>
       <c r="H35" t="s">
         <v>46</v>
@@ -5555,7 +5564,7 @@
       </c>
       <c r="G36" s="3">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>748</v>
@@ -5610,7 +5619,7 @@
       </c>
       <c r="G37" s="3">
         <f t="shared" si="0"/>
-        <v>56.099999999999994</v>
+        <v>55.8</v>
       </c>
       <c r="H37" t="s">
         <v>48</v>
@@ -5665,7 +5674,7 @@
       </c>
       <c r="G38" s="3">
         <f t="shared" si="0"/>
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="H38" t="s">
         <v>49</v>
@@ -5720,7 +5729,7 @@
       </c>
       <c r="G39" s="3">
         <f t="shared" si="0"/>
-        <v>47.199999999999996</v>
+        <v>46.9</v>
       </c>
       <c r="H39" t="s">
         <v>50</v>
@@ -5775,7 +5784,7 @@
       </c>
       <c r="G40" s="3">
         <f t="shared" si="0"/>
-        <v>36.699999999999996</v>
+        <v>36.4</v>
       </c>
       <c r="H40" t="s">
         <v>51</v>
@@ -5830,7 +5839,7 @@
       </c>
       <c r="G41" s="3">
         <f t="shared" si="0"/>
-        <v>42.599999999999994</v>
+        <v>42.3</v>
       </c>
       <c r="H41" t="s">
         <v>52</v>
@@ -5885,7 +5894,7 @@
       </c>
       <c r="G42" s="3">
         <f t="shared" si="0"/>
-        <v>-23.900000000000002</v>
+        <v>-24.200000000000003</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>752</v>
@@ -5940,7 +5949,7 @@
       </c>
       <c r="G43" s="3">
         <f t="shared" si="0"/>
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
         <v>54</v>
@@ -5995,7 +6004,7 @@
       </c>
       <c r="G44" s="3">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>793</v>
@@ -6050,7 +6059,7 @@
       </c>
       <c r="G45" s="3">
         <f t="shared" si="0"/>
-        <v>-11</v>
+        <v>-11.3</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>772</v>
@@ -6105,7 +6114,7 @@
       </c>
       <c r="G46" s="3">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>32.9</v>
       </c>
       <c r="H46" t="s">
         <v>57</v>
@@ -6161,7 +6170,7 @@
       </c>
       <c r="G47" s="3">
         <f t="shared" si="0"/>
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -6216,7 +6225,7 @@
       </c>
       <c r="G48" s="3">
         <f t="shared" si="0"/>
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>734</v>
@@ -6271,7 +6280,7 @@
       </c>
       <c r="G49" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="H49" t="s">
         <v>60</v>
@@ -6327,7 +6336,7 @@
       </c>
       <c r="G50" s="3">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H50" t="s">
         <v>61</v>
@@ -6382,7 +6391,7 @@
       </c>
       <c r="G51" s="3">
         <f t="shared" si="0"/>
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="H51" t="s">
         <v>62</v>
@@ -6437,7 +6446,7 @@
       </c>
       <c r="G52" s="3">
         <f t="shared" si="0"/>
-        <v>48.199999999999996</v>
+        <v>47.9</v>
       </c>
       <c r="H52" t="s">
         <v>63</v>
@@ -6492,7 +6501,7 @@
       </c>
       <c r="G53" s="3">
         <f t="shared" si="0"/>
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="H53" t="s">
         <v>64</v>
@@ -6547,7 +6556,7 @@
       </c>
       <c r="G54" s="3">
         <f t="shared" si="0"/>
-        <v>33.299999999999997</v>
+        <v>33</v>
       </c>
       <c r="H54" t="s">
         <v>65</v>
@@ -6602,7 +6611,7 @@
       </c>
       <c r="G55" s="3">
         <f t="shared" si="0"/>
-        <v>18.100000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="H55" t="s">
         <v>66</v>
@@ -6657,7 +6666,7 @@
       </c>
       <c r="G56" s="3">
         <f t="shared" si="0"/>
-        <v>58.9</v>
+        <v>58.6</v>
       </c>
       <c r="H56" t="s">
         <v>67</v>
@@ -6712,7 +6721,7 @@
       </c>
       <c r="G57" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="H57" t="s">
         <v>68</v>
@@ -6768,7 +6777,7 @@
       </c>
       <c r="G58" s="3">
         <f t="shared" si="0"/>
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s">
         <v>69</v>
@@ -6823,7 +6832,7 @@
       </c>
       <c r="G59" s="3">
         <f t="shared" si="0"/>
-        <v>68.7</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="H59" t="s">
         <v>70</v>
@@ -6878,7 +6887,7 @@
       </c>
       <c r="G60" s="3">
         <f t="shared" si="0"/>
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>731</v>
@@ -6934,7 +6943,7 @@
       </c>
       <c r="G61" s="3">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="H61" t="s">
         <v>71</v>
@@ -6990,7 +6999,7 @@
       </c>
       <c r="G62" s="3">
         <f t="shared" si="0"/>
-        <v>-3.8999999999999995</v>
+        <v>-4.1999999999999993</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>756</v>
@@ -7045,7 +7054,7 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="0"/>
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="H63" t="s">
         <v>73</v>
@@ -7100,7 +7109,7 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="0"/>
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H64" t="s">
         <v>74</v>
@@ -7155,7 +7164,7 @@
       </c>
       <c r="G65" s="3">
         <f t="shared" si="0"/>
-        <v>57.199999999999996</v>
+        <v>56.9</v>
       </c>
       <c r="H65" t="s">
         <v>75</v>
@@ -7210,7 +7219,7 @@
       </c>
       <c r="G66" s="3">
         <f t="shared" si="0"/>
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="H66" t="s">
         <v>76</v>
@@ -7265,8 +7274,8 @@
         <v>10.100000000000001</v>
       </c>
       <c r="G67" s="3">
-        <f t="shared" ref="G67:G130" si="1">E67+6.8+1.5</f>
-        <v>12.2</v>
+        <f t="shared" ref="G67:G130" si="1">E67+6.5+1.5</f>
+        <v>11.9</v>
       </c>
       <c r="H67" t="s">
         <v>77</v>
@@ -7321,7 +7330,7 @@
       </c>
       <c r="G68" s="3">
         <f t="shared" si="1"/>
-        <v>24.400000000000002</v>
+        <v>24.1</v>
       </c>
       <c r="H68" t="s">
         <v>78</v>
@@ -7376,7 +7385,7 @@
       </c>
       <c r="G69" s="3">
         <f t="shared" si="1"/>
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="H69" t="s">
         <v>79</v>
@@ -7431,7 +7440,7 @@
       </c>
       <c r="G70" s="3">
         <f t="shared" si="1"/>
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>760</v>
@@ -7487,7 +7496,7 @@
       </c>
       <c r="G71" s="3">
         <f t="shared" si="1"/>
-        <v>20.399999999999999</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="H71" t="s">
         <v>81</v>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="G72" s="3">
         <f t="shared" si="1"/>
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="H72" t="s">
         <v>82</v>
@@ -7597,7 +7606,7 @@
       </c>
       <c r="G73" s="3">
         <f t="shared" si="1"/>
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="H73" t="s">
         <v>83</v>
@@ -7652,7 +7661,7 @@
       </c>
       <c r="G74" s="3">
         <f t="shared" si="1"/>
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="H74" t="s">
         <v>84</v>
@@ -7707,7 +7716,7 @@
       </c>
       <c r="G75" s="3">
         <f t="shared" si="1"/>
-        <v>64.199999999999989</v>
+        <v>63.9</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>885</v>
@@ -7762,7 +7771,7 @@
       </c>
       <c r="G76" s="3">
         <f t="shared" si="1"/>
-        <v>48.099999999999994</v>
+        <v>47.8</v>
       </c>
       <c r="H76" t="s">
         <v>86</v>
@@ -7817,7 +7826,7 @@
       </c>
       <c r="G77" s="3">
         <f t="shared" si="1"/>
-        <v>-1.3999999999999995</v>
+        <v>-1.6999999999999993</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>888</v>
@@ -7872,7 +7881,7 @@
       </c>
       <c r="G78" s="3">
         <f t="shared" si="1"/>
-        <v>-10</v>
+        <v>-10.3</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>889</v>
@@ -7927,7 +7936,7 @@
       </c>
       <c r="G79" s="3">
         <f t="shared" si="1"/>
-        <v>-0.79999999999999982</v>
+        <v>-1.0999999999999996</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>890</v>
@@ -7982,7 +7991,7 @@
       </c>
       <c r="G80" s="3">
         <f t="shared" si="1"/>
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>90</v>
@@ -8037,7 +8046,7 @@
       </c>
       <c r="G81" s="3">
         <f t="shared" si="1"/>
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>91</v>
@@ -8092,7 +8101,7 @@
       </c>
       <c r="G82" s="3">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>893</v>
@@ -8147,7 +8156,7 @@
       </c>
       <c r="G83" s="3">
         <f t="shared" si="1"/>
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>973</v>
@@ -8202,7 +8211,7 @@
       </c>
       <c r="G84" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="H84" t="s">
         <v>94</v>
@@ -8257,7 +8266,7 @@
       </c>
       <c r="G85" s="3">
         <f t="shared" si="1"/>
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="H85" t="s">
         <v>95</v>
@@ -8312,7 +8321,7 @@
       </c>
       <c r="G86" s="3">
         <f t="shared" si="1"/>
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="H86" t="s">
         <v>96</v>
@@ -8367,7 +8376,7 @@
       </c>
       <c r="G87" s="3">
         <f t="shared" si="1"/>
-        <v>13.899999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="H87" t="s">
         <v>97</v>
@@ -8422,7 +8431,7 @@
       </c>
       <c r="G88" s="3">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="K88" t="s">
         <v>674</v>
@@ -8472,7 +8481,7 @@
       </c>
       <c r="G89" s="3">
         <f t="shared" si="1"/>
-        <v>-28.600000000000005</v>
+        <v>-28.900000000000006</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>1014</v>
@@ -8528,7 +8537,7 @@
       </c>
       <c r="G90" s="3">
         <f t="shared" si="1"/>
-        <v>-9.6999999999999993</v>
+        <v>-10</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>1027</v>
@@ -8584,7 +8593,7 @@
       </c>
       <c r="G91" s="3">
         <f t="shared" si="1"/>
-        <v>-12.599999999999998</v>
+        <v>-12.899999999999999</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>1018</v>
@@ -8640,7 +8649,7 @@
       </c>
       <c r="G92" s="3">
         <f t="shared" si="1"/>
-        <v>-3.5000000000000044</v>
+        <v>-3.8000000000000043</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>1004</v>
@@ -8696,7 +8705,7 @@
       </c>
       <c r="G93" s="3">
         <f t="shared" si="1"/>
-        <v>-13.099999999999998</v>
+        <v>-13.399999999999999</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>995</v>
@@ -8752,7 +8761,7 @@
       </c>
       <c r="G94" s="3">
         <f t="shared" si="1"/>
-        <v>-21.7</v>
+        <v>-22</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>1023</v>
@@ -8808,7 +8817,7 @@
       </c>
       <c r="G95" s="3">
         <f t="shared" si="1"/>
-        <v>-4.0999999999999988</v>
+        <v>-4.3999999999999986</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>1011</v>
@@ -8864,7 +8873,7 @@
       </c>
       <c r="G96" s="3">
         <f t="shared" si="1"/>
-        <v>-7.7999999999999936</v>
+        <v>-8.0999999999999943</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>996</v>
@@ -8920,7 +8929,7 @@
       </c>
       <c r="G97" s="3">
         <f t="shared" si="1"/>
-        <v>-9.4000000000000021</v>
+        <v>-9.7000000000000028</v>
       </c>
       <c r="H97" t="s">
         <v>107</v>
@@ -8976,7 +8985,7 @@
       </c>
       <c r="G98" s="3">
         <f t="shared" si="1"/>
-        <v>32.200000000000003</v>
+        <v>31.9</v>
       </c>
       <c r="H98" t="s">
         <v>108</v>
@@ -9029,7 +9038,7 @@
       </c>
       <c r="G99" s="3">
         <f t="shared" si="1"/>
-        <v>-7.4000000000000021</v>
+        <v>-7.7000000000000028</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>1007</v>
@@ -9085,7 +9094,7 @@
       </c>
       <c r="G100" s="3">
         <f t="shared" si="1"/>
-        <v>-6.9999999999999964</v>
+        <v>-7.2999999999999972</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>1019</v>
@@ -9141,7 +9150,7 @@
       </c>
       <c r="G101" s="3">
         <f t="shared" si="1"/>
-        <v>-5.4999999999999973</v>
+        <v>-5.7999999999999972</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>998</v>
@@ -9197,7 +9206,7 @@
       </c>
       <c r="G102" s="3">
         <f t="shared" si="1"/>
-        <v>-2.2000000000000002</v>
+        <v>-2.5</v>
       </c>
       <c r="H102" t="s">
         <v>112</v>
@@ -9253,7 +9262,7 @@
       </c>
       <c r="G103" s="3">
         <f t="shared" si="1"/>
-        <v>-11.500000000000004</v>
+        <v>-11.800000000000004</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>1020</v>
@@ -9309,7 +9318,7 @@
       </c>
       <c r="G104" s="3">
         <f t="shared" si="1"/>
-        <v>-5.3000000000000016</v>
+        <v>-5.6000000000000014</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>1022</v>
@@ -9365,7 +9374,7 @@
       </c>
       <c r="G105" s="3">
         <f t="shared" si="1"/>
-        <v>-13.7</v>
+        <v>-14</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>1013</v>
@@ -9421,7 +9430,7 @@
       </c>
       <c r="G106" s="3">
         <f t="shared" si="1"/>
-        <v>-8.5999999999999979</v>
+        <v>-8.8999999999999986</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>1024</v>
@@ -9477,7 +9486,7 @@
       </c>
       <c r="G107" s="3">
         <f t="shared" si="1"/>
-        <v>-22.700000000000006</v>
+        <v>-23.000000000000007</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>1016</v>
@@ -9533,7 +9542,7 @@
       </c>
       <c r="G108" s="3">
         <f t="shared" si="1"/>
-        <v>45.300000000000004</v>
+        <v>45.000000000000007</v>
       </c>
       <c r="H108" t="s">
         <v>122</v>
@@ -9589,7 +9598,7 @@
       </c>
       <c r="G109" s="3">
         <f t="shared" si="1"/>
-        <v>-7.9000000000000021</v>
+        <v>-8.2000000000000028</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>1031</v>
@@ -9645,7 +9654,7 @@
       </c>
       <c r="G110" s="3">
         <f t="shared" si="1"/>
-        <v>-2.2000000000000002</v>
+        <v>-2.5</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>1000</v>
@@ -9701,7 +9710,7 @@
       </c>
       <c r="G111" s="3">
         <f t="shared" si="1"/>
-        <v>22.099999999999998</v>
+        <v>21.799999999999997</v>
       </c>
       <c r="H111" t="s">
         <v>119</v>
@@ -9757,7 +9766,7 @@
       </c>
       <c r="G112" s="3">
         <f t="shared" si="1"/>
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>1026</v>
@@ -9813,7 +9822,7 @@
       </c>
       <c r="G113" s="3">
         <f t="shared" si="1"/>
-        <v>-0.90000000000000302</v>
+        <v>-1.2000000000000028</v>
       </c>
       <c r="H113" t="s">
         <v>120</v>
@@ -9869,7 +9878,7 @@
       </c>
       <c r="G114" s="3">
         <f t="shared" si="1"/>
-        <v>-10.000000000000004</v>
+        <v>-10.300000000000004</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>1002</v>
@@ -9925,7 +9934,7 @@
       </c>
       <c r="G115" s="3">
         <f t="shared" si="1"/>
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>1025</v>
@@ -9981,7 +9990,7 @@
       </c>
       <c r="G116" s="3">
         <f t="shared" si="1"/>
-        <v>-17.100000000000005</v>
+        <v>-17.400000000000006</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>1003</v>
@@ -10036,7 +10045,7 @@
       </c>
       <c r="G117" s="3">
         <f t="shared" si="1"/>
-        <v>-7.3999999999999986</v>
+        <v>-7.6999999999999993</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>822</v>
@@ -10091,7 +10100,7 @@
       </c>
       <c r="G118" s="3">
         <f t="shared" si="1"/>
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="H118" t="s">
         <v>127</v>
@@ -10147,7 +10156,7 @@
       </c>
       <c r="G119" s="3">
         <f t="shared" si="1"/>
-        <v>-22.7</v>
+        <v>-23</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>130</v>
@@ -10202,7 +10211,7 @@
       </c>
       <c r="G120" s="3">
         <f t="shared" si="1"/>
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="H120" t="s">
         <v>131</v>
@@ -10258,7 +10267,7 @@
       </c>
       <c r="G121" s="3">
         <f t="shared" si="1"/>
-        <v>80.399999999999991</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="H121" t="s">
         <v>133</v>
@@ -10314,7 +10323,7 @@
       </c>
       <c r="G122" s="3">
         <f t="shared" si="1"/>
-        <v>58.3</v>
+        <v>58</v>
       </c>
       <c r="H122" t="s">
         <v>135</v>
@@ -10369,7 +10378,7 @@
       </c>
       <c r="G123" s="3">
         <f t="shared" si="1"/>
-        <v>-12.8</v>
+        <v>-13.100000000000001</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>825</v>
@@ -10425,7 +10434,7 @@
       </c>
       <c r="G124" s="3">
         <f t="shared" si="1"/>
-        <v>-23</v>
+        <v>-23.3</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>138</v>
@@ -10481,7 +10490,7 @@
       </c>
       <c r="G125" s="3">
         <f t="shared" si="1"/>
-        <v>-26.599999999999998</v>
+        <v>-26.9</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>140</v>
@@ -10537,7 +10546,7 @@
       </c>
       <c r="G126" s="3">
         <f t="shared" si="1"/>
-        <v>-13.599999999999998</v>
+        <v>-13.899999999999999</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>826</v>
@@ -10593,7 +10602,7 @@
       </c>
       <c r="G127" s="3">
         <f t="shared" si="1"/>
-        <v>-15.399999999999999</v>
+        <v>-15.7</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>144</v>
@@ -10648,7 +10657,7 @@
       </c>
       <c r="G128" s="3">
         <f t="shared" si="1"/>
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>828</v>
@@ -10703,7 +10712,7 @@
       </c>
       <c r="G129" s="3">
         <f t="shared" si="1"/>
-        <v>50.699999999999996</v>
+        <v>50.4</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>146</v>
@@ -10759,7 +10768,7 @@
       </c>
       <c r="G130" s="3">
         <f t="shared" si="1"/>
-        <v>-29.099999999999998</v>
+        <v>-29.4</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>149</v>
@@ -10813,8 +10822,8 @@
         <v>29.4</v>
       </c>
       <c r="G131" s="3">
-        <f t="shared" ref="G131:G194" si="2">E131+6.8+1.5</f>
-        <v>33</v>
+        <f t="shared" ref="G131:G194" si="2">E131+6.5+1.5</f>
+        <v>32.700000000000003</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>150</v>
@@ -10869,7 +10878,7 @@
       </c>
       <c r="G132" s="3">
         <f t="shared" si="2"/>
-        <v>29.900000000000002</v>
+        <v>29.6</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>151</v>
@@ -10924,7 +10933,7 @@
       </c>
       <c r="G133" s="3">
         <f t="shared" si="2"/>
-        <v>-36.800000000000004</v>
+        <v>-37.1</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>153</v>
@@ -10979,7 +10988,7 @@
       </c>
       <c r="G134" s="3">
         <f t="shared" si="2"/>
-        <v>-18.399999999999999</v>
+        <v>-18.7</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>155</v>
@@ -11034,7 +11043,7 @@
       </c>
       <c r="G135" s="3">
         <f t="shared" si="2"/>
-        <v>40.299999999999997</v>
+        <v>40</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>156</v>
@@ -11090,7 +11099,7 @@
       </c>
       <c r="G136" s="3">
         <f t="shared" si="2"/>
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>159</v>
@@ -11146,7 +11155,7 @@
       </c>
       <c r="G137" s="3">
         <f t="shared" si="2"/>
-        <v>39.5</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>161</v>
@@ -11202,7 +11211,7 @@
       </c>
       <c r="G138" s="3">
         <f t="shared" si="2"/>
-        <v>36.6</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>164</v>
@@ -11258,7 +11267,7 @@
       </c>
       <c r="G139" s="3">
         <f t="shared" si="2"/>
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>166</v>
@@ -11314,7 +11323,7 @@
       </c>
       <c r="G140" s="3">
         <f t="shared" si="2"/>
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>168</v>
@@ -11370,7 +11379,7 @@
       </c>
       <c r="G141" s="3">
         <f t="shared" si="2"/>
-        <v>73.8</v>
+        <v>73.5</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>171</v>
@@ -11426,7 +11435,7 @@
       </c>
       <c r="G142" s="3">
         <f t="shared" si="2"/>
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>174</v>
@@ -11482,7 +11491,7 @@
       </c>
       <c r="G143" s="3">
         <f t="shared" si="2"/>
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>177</v>
@@ -11538,7 +11547,7 @@
       </c>
       <c r="G144" s="3">
         <f t="shared" si="2"/>
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>179</v>
@@ -11594,7 +11603,7 @@
       </c>
       <c r="G145" s="3">
         <f t="shared" si="2"/>
-        <v>19.7</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>181</v>
@@ -11650,7 +11659,7 @@
       </c>
       <c r="G146" s="3">
         <f t="shared" si="2"/>
-        <v>-35.200000000000003</v>
+        <v>-35.5</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>184</v>
@@ -11705,7 +11714,7 @@
       </c>
       <c r="G147" s="3">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="H147" s="6" t="s">
         <v>185</v>
@@ -11761,7 +11770,7 @@
       </c>
       <c r="G148" s="3">
         <f t="shared" si="2"/>
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="H148" s="6" t="s">
         <v>187</v>
@@ -11817,7 +11826,7 @@
       </c>
       <c r="G149" s="3">
         <f t="shared" si="2"/>
-        <v>-31.6</v>
+        <v>-31.9</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>190</v>
@@ -11873,7 +11882,7 @@
       </c>
       <c r="G150" s="3">
         <f t="shared" si="2"/>
-        <v>-14.399999999999999</v>
+        <v>-14.7</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>192</v>
@@ -11929,7 +11938,7 @@
       </c>
       <c r="G151" s="3">
         <f t="shared" si="2"/>
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="H151" t="s">
         <v>193</v>
@@ -11985,7 +11994,7 @@
       </c>
       <c r="G152" s="3">
         <f t="shared" si="2"/>
-        <v>8.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H152" t="s">
         <v>195</v>
@@ -12041,7 +12050,7 @@
       </c>
       <c r="G153" s="3">
         <f t="shared" si="2"/>
-        <v>-18.099999999999998</v>
+        <v>-18.399999999999999</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>198</v>
@@ -12097,7 +12106,7 @@
       </c>
       <c r="G154" s="3">
         <f t="shared" si="2"/>
-        <v>-23.3</v>
+        <v>-23.6</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>200</v>
@@ -12153,7 +12162,7 @@
       </c>
       <c r="G155" s="3">
         <f t="shared" si="2"/>
-        <v>-21.4</v>
+        <v>-21.7</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>202</v>
@@ -12209,7 +12218,7 @@
       </c>
       <c r="G156" s="3">
         <f t="shared" si="2"/>
-        <v>-8.3999999999999986</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>204</v>
@@ -12265,7 +12274,7 @@
       </c>
       <c r="G157" s="3">
         <f t="shared" si="2"/>
-        <v>-24.8</v>
+        <v>-25.1</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>206</v>
@@ -12321,7 +12330,7 @@
       </c>
       <c r="G158" s="3">
         <f t="shared" si="2"/>
-        <v>49.699999999999996</v>
+        <v>49.4</v>
       </c>
       <c r="H158" s="6" t="s">
         <v>207</v>
@@ -12377,7 +12386,7 @@
       </c>
       <c r="G159" s="3">
         <f t="shared" si="2"/>
-        <v>-28.2</v>
+        <v>-28.5</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>210</v>
@@ -12433,7 +12442,7 @@
       </c>
       <c r="G160" s="3">
         <f t="shared" si="2"/>
-        <v>-22.099999999999998</v>
+        <v>-22.4</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>212</v>
@@ -12489,7 +12498,7 @@
       </c>
       <c r="G161" s="3">
         <f t="shared" si="2"/>
-        <v>-0.20000000000000018</v>
+        <v>-0.5</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>717</v>
@@ -12545,7 +12554,7 @@
       </c>
       <c r="G162" s="3">
         <f t="shared" si="2"/>
-        <v>-1.7000000000000002</v>
+        <v>-2</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>719</v>
@@ -12601,7 +12610,7 @@
       </c>
       <c r="G163" s="3">
         <f t="shared" si="2"/>
-        <v>3.8999999999999995</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>721</v>
@@ -12657,7 +12666,7 @@
       </c>
       <c r="G164" s="3">
         <f t="shared" si="2"/>
-        <v>-23.2</v>
+        <v>-23.5</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>730</v>
@@ -12713,7 +12722,7 @@
       </c>
       <c r="G165" s="3">
         <f t="shared" si="2"/>
-        <v>-23</v>
+        <v>-23.3</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>943</v>
@@ -12768,7 +12777,7 @@
       </c>
       <c r="G166" s="3">
         <f t="shared" si="2"/>
-        <v>-11.399999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>913</v>
@@ -12823,7 +12832,7 @@
       </c>
       <c r="G167" s="3">
         <f t="shared" si="2"/>
-        <v>12.399999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="H167" s="6" t="s">
         <v>219</v>
@@ -12878,7 +12887,7 @@
       </c>
       <c r="G168" s="3">
         <f t="shared" si="2"/>
-        <v>-15</v>
+        <v>-15.3</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>944</v>
@@ -12933,7 +12942,7 @@
       </c>
       <c r="G169" s="3">
         <f t="shared" si="2"/>
-        <v>-39</v>
+        <v>-39.299999999999997</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>222</v>
@@ -12988,7 +12997,7 @@
       </c>
       <c r="G170" s="3">
         <f t="shared" si="2"/>
-        <v>-33</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>224</v>
@@ -13043,7 +13052,7 @@
       </c>
       <c r="G171" s="3">
         <f t="shared" si="2"/>
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="H171" t="s">
         <v>225</v>
@@ -13099,7 +13108,7 @@
       </c>
       <c r="G172" s="3">
         <f t="shared" si="2"/>
-        <v>-27.2</v>
+        <v>-27.5</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>228</v>
@@ -13155,7 +13164,7 @@
       </c>
       <c r="G173" s="3">
         <f t="shared" si="2"/>
-        <v>-55.6</v>
+        <v>-55.9</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>231</v>
@@ -13210,7 +13219,7 @@
       </c>
       <c r="G174" s="3">
         <f t="shared" si="2"/>
-        <v>-6.6999999999999993</v>
+        <v>-7</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>233</v>
@@ -13267,7 +13276,7 @@
       </c>
       <c r="G175" s="3">
         <f t="shared" si="2"/>
-        <v>-30.099999999999998</v>
+        <v>-30.4</v>
       </c>
       <c r="K175" t="s">
         <v>672</v>
@@ -13305,7 +13314,7 @@
       </c>
       <c r="G176" s="3">
         <f t="shared" si="2"/>
-        <v>55.999999999999993</v>
+        <v>55.699999999999996</v>
       </c>
       <c r="K176" t="s">
         <v>672</v>
@@ -13343,7 +13352,7 @@
       </c>
       <c r="G177" s="3">
         <f t="shared" si="2"/>
-        <v>-27.900000000000002</v>
+        <v>-28.200000000000003</v>
       </c>
       <c r="K177" t="s">
         <v>672</v>
@@ -13381,7 +13390,7 @@
       </c>
       <c r="G178" s="3">
         <f t="shared" si="2"/>
-        <v>-25.900000000000002</v>
+        <v>-26.200000000000003</v>
       </c>
       <c r="K178" t="s">
         <v>672</v>
@@ -13419,7 +13428,7 @@
       </c>
       <c r="G179" s="3">
         <f t="shared" si="2"/>
-        <v>-25.700000000000006</v>
+        <v>-26.000000000000007</v>
       </c>
       <c r="K179" t="s">
         <v>672</v>
@@ -13457,7 +13466,7 @@
       </c>
       <c r="G180" s="3">
         <f t="shared" si="2"/>
-        <v>-23.499999999999996</v>
+        <v>-23.799999999999997</v>
       </c>
       <c r="K180" t="s">
         <v>672</v>
@@ -13494,7 +13503,7 @@
       </c>
       <c r="G181" s="3">
         <f t="shared" si="2"/>
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="H181" t="s">
         <v>241</v>
@@ -13549,7 +13558,7 @@
       </c>
       <c r="G182" s="3">
         <f t="shared" si="2"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.5</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>829</v>
@@ -13604,7 +13613,7 @@
       </c>
       <c r="G183" s="3">
         <f t="shared" si="2"/>
-        <v>-8.5</v>
+        <v>-8.8000000000000007</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>863</v>
@@ -13659,7 +13668,7 @@
       </c>
       <c r="G184" s="3">
         <f t="shared" si="2"/>
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="H184" t="s">
         <v>244</v>
@@ -13714,7 +13723,7 @@
       </c>
       <c r="G185" s="3">
         <f t="shared" si="2"/>
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="H185" t="s">
         <v>245</v>
@@ -13769,7 +13778,7 @@
       </c>
       <c r="G186" s="3">
         <f t="shared" si="2"/>
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="H186" t="s">
         <v>246</v>
@@ -13824,7 +13833,7 @@
       </c>
       <c r="G187" s="3">
         <f t="shared" si="2"/>
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>864</v>
@@ -13879,7 +13888,7 @@
       </c>
       <c r="G188" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H188" t="s">
         <v>248</v>
@@ -13934,7 +13943,7 @@
       </c>
       <c r="G189" s="3">
         <f t="shared" si="2"/>
-        <v>66.900000000000006</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="H189" t="s">
         <v>249</v>
@@ -13989,7 +13998,7 @@
       </c>
       <c r="G190" s="3">
         <f t="shared" si="2"/>
-        <v>64.099999999999994</v>
+        <v>63.8</v>
       </c>
       <c r="H190" t="s">
         <v>250</v>
@@ -14044,7 +14053,7 @@
       </c>
       <c r="G191" s="3">
         <f t="shared" si="2"/>
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="H191" t="s">
         <v>251</v>
@@ -14096,7 +14105,7 @@
       </c>
       <c r="G192" s="3">
         <f t="shared" si="2"/>
-        <v>31.900000000000002</v>
+        <v>31.6</v>
       </c>
       <c r="H192" t="s">
         <v>690</v>
@@ -14148,7 +14157,7 @@
       </c>
       <c r="G193" s="3">
         <f t="shared" si="2"/>
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="H193" t="s">
         <v>252</v>
@@ -14203,7 +14212,7 @@
       </c>
       <c r="G194" s="3">
         <f t="shared" si="2"/>
-        <v>27.900000000000002</v>
+        <v>27.6</v>
       </c>
       <c r="H194" t="s">
         <v>253</v>
@@ -14257,8 +14266,8 @@
         <v>50.900000000000006</v>
       </c>
       <c r="G195" s="3">
-        <f t="shared" ref="G195:G258" si="3">E195+6.8+1.5</f>
-        <v>53.199999999999996</v>
+        <f t="shared" ref="G195:G258" si="3">E195+6.5+1.5</f>
+        <v>52.9</v>
       </c>
       <c r="H195" t="s">
         <v>1045</v>
@@ -14310,7 +14319,7 @@
       </c>
       <c r="G196" s="3">
         <f t="shared" si="3"/>
-        <v>28.900000000000002</v>
+        <v>28.6</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>1046</v>
@@ -14365,7 +14374,7 @@
       </c>
       <c r="G197" s="3">
         <f t="shared" si="3"/>
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="H197" t="s">
         <v>256</v>
@@ -14417,7 +14426,7 @@
       </c>
       <c r="G198" s="3">
         <f t="shared" si="3"/>
-        <v>34.5</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="H198" t="s">
         <v>257</v>
@@ -14472,7 +14481,7 @@
       </c>
       <c r="G199" s="3">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="H199" t="s">
         <v>258</v>
@@ -14527,7 +14536,7 @@
       </c>
       <c r="G200" s="3">
         <f t="shared" si="3"/>
-        <v>-12.899999999999999</v>
+        <v>-13.2</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>942</v>
@@ -14582,7 +14591,7 @@
       </c>
       <c r="G201" s="3">
         <f t="shared" si="3"/>
-        <v>-21.599999999999998</v>
+        <v>-21.9</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>960</v>
@@ -14637,7 +14646,7 @@
       </c>
       <c r="G202" s="3">
         <f t="shared" si="3"/>
-        <v>16.100000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="H202" t="s">
         <v>261</v>
@@ -14692,7 +14701,7 @@
       </c>
       <c r="G203" s="3">
         <f t="shared" si="3"/>
-        <v>2.5999999999999996</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>934</v>
@@ -14747,7 +14756,7 @@
       </c>
       <c r="G204" s="3">
         <f t="shared" si="3"/>
-        <v>-18.8</v>
+        <v>-19.100000000000001</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>907</v>
@@ -14802,7 +14811,7 @@
       </c>
       <c r="G205" s="3">
         <f t="shared" si="3"/>
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="H205" t="s">
         <v>264</v>
@@ -14857,7 +14866,7 @@
       </c>
       <c r="G206" s="3">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>928</v>
@@ -14912,7 +14921,7 @@
       </c>
       <c r="G207" s="3">
         <f t="shared" si="3"/>
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H207" t="s">
         <v>266</v>
@@ -14967,7 +14976,7 @@
       </c>
       <c r="G208" s="3">
         <f t="shared" si="3"/>
-        <v>-23.999999999999996</v>
+        <v>-24.299999999999997</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>909</v>
@@ -15022,7 +15031,7 @@
       </c>
       <c r="G209" s="3">
         <f t="shared" si="3"/>
-        <v>1.7999999999999998</v>
+        <v>1.5</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>939</v>
@@ -15077,7 +15086,7 @@
       </c>
       <c r="G210" s="3">
         <f t="shared" si="3"/>
-        <v>24.400000000000002</v>
+        <v>24.1</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>919</v>
@@ -15132,7 +15141,7 @@
       </c>
       <c r="G211" s="3">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="H211" t="s">
         <v>270</v>
@@ -15187,7 +15196,7 @@
       </c>
       <c r="G212" s="3">
         <f t="shared" si="3"/>
-        <v>49.699999999999996</v>
+        <v>49.4</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>945</v>
@@ -15242,7 +15251,7 @@
       </c>
       <c r="G213" s="3">
         <f t="shared" si="3"/>
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>981</v>
@@ -15297,7 +15306,7 @@
       </c>
       <c r="G214" s="3">
         <f t="shared" si="3"/>
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>979</v>
@@ -15352,7 +15361,7 @@
       </c>
       <c r="G215" s="3">
         <f t="shared" si="3"/>
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="H215" s="6" t="s">
         <v>274</v>
@@ -15407,7 +15416,7 @@
       </c>
       <c r="G216" s="3">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="H216" t="s">
         <v>275</v>
@@ -15462,7 +15471,7 @@
       </c>
       <c r="G217" s="3">
         <f t="shared" si="3"/>
-        <v>70.2</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="H217" s="6" t="s">
         <v>276</v>
@@ -15517,7 +15526,7 @@
       </c>
       <c r="G218" s="3">
         <f t="shared" si="3"/>
-        <v>-11.399999999999999</v>
+        <v>-11.7</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>982</v>
@@ -15572,7 +15581,7 @@
       </c>
       <c r="G219" s="3">
         <f t="shared" si="3"/>
-        <v>-28.2</v>
+        <v>-28.5</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>985</v>
@@ -15627,7 +15636,7 @@
       </c>
       <c r="G220" s="3">
         <f t="shared" si="3"/>
-        <v>-6.0000000000000009</v>
+        <v>-6.3000000000000007</v>
       </c>
       <c r="H220" t="s">
         <v>980</v>
@@ -15682,7 +15691,7 @@
       </c>
       <c r="G221" s="3">
         <f t="shared" si="3"/>
-        <v>-28.7</v>
+        <v>-29</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>281</v>
@@ -15737,7 +15746,7 @@
       </c>
       <c r="G222" s="3">
         <f t="shared" si="3"/>
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="H222" t="s">
         <v>282</v>
@@ -15793,7 +15802,7 @@
       </c>
       <c r="G223" s="3">
         <f t="shared" si="3"/>
-        <v>-20.9</v>
+        <v>-21.2</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>285</v>
@@ -15848,7 +15857,7 @@
       </c>
       <c r="G224" s="3">
         <f t="shared" si="3"/>
-        <v>-34.200000000000003</v>
+        <v>-34.5</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>287</v>
@@ -15904,7 +15913,7 @@
       </c>
       <c r="G225" s="3">
         <f t="shared" si="3"/>
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
       <c r="H225" s="6" t="s">
         <v>288</v>
@@ -15960,7 +15969,7 @@
       </c>
       <c r="G226" s="3">
         <f t="shared" si="3"/>
-        <v>0.40000000000000124</v>
+        <v>0.10000000000000142</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>940</v>
@@ -16016,7 +16025,7 @@
       </c>
       <c r="G227" s="3">
         <f t="shared" si="3"/>
-        <v>-18.400000000000002</v>
+        <v>-18.700000000000003</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>918</v>
@@ -16072,7 +16081,7 @@
       </c>
       <c r="G228" s="3">
         <f t="shared" si="3"/>
-        <v>-33.800000000000011</v>
+        <v>-34.100000000000009</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>937</v>
@@ -16128,7 +16137,7 @@
       </c>
       <c r="G229" s="3">
         <f t="shared" si="3"/>
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="H229" t="s">
         <v>915</v>
@@ -16184,7 +16193,7 @@
       </c>
       <c r="G230" s="3">
         <f t="shared" si="3"/>
-        <v>-30.299999999999994</v>
+        <v>-30.599999999999994</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>923</v>
@@ -16240,7 +16249,7 @@
       </c>
       <c r="G231" s="3">
         <f t="shared" si="3"/>
-        <v>-34.300000000000004</v>
+        <v>-34.6</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>916</v>
@@ -16295,8 +16304,8 @@
         <v>-51.300000000000004</v>
       </c>
       <c r="G232" s="3">
-        <f>E232+6.8+1.5</f>
-        <v>-45.6</v>
+        <f t="shared" si="3"/>
+        <v>-45.9</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>938</v>
@@ -16351,7 +16360,7 @@
       </c>
       <c r="G233" s="3">
         <f t="shared" si="3"/>
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>764</v>
@@ -16407,7 +16416,7 @@
       </c>
       <c r="G234" s="3">
         <f t="shared" si="3"/>
-        <v>-21.2</v>
+        <v>-21.5</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>763</v>
@@ -16463,7 +16472,7 @@
       </c>
       <c r="G235" s="3">
         <f t="shared" si="3"/>
-        <v>-4.8</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>299</v>
@@ -16518,7 +16527,7 @@
       </c>
       <c r="G236" s="3">
         <f t="shared" si="3"/>
-        <v>12.899999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>301</v>
@@ -16574,7 +16583,7 @@
       </c>
       <c r="G237" s="3">
         <f t="shared" si="3"/>
-        <v>-45.5</v>
+        <v>-45.8</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>304</v>
@@ -16629,7 +16638,7 @@
       </c>
       <c r="G238" s="3">
         <f t="shared" si="3"/>
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="H238" s="6" t="s">
         <v>305</v>
@@ -16684,7 +16693,7 @@
       </c>
       <c r="G239" s="3">
         <f t="shared" si="3"/>
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>801</v>
@@ -16739,7 +16748,7 @@
       </c>
       <c r="G240" s="3">
         <f t="shared" si="3"/>
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H240" s="6" t="s">
         <v>307</v>
@@ -16794,7 +16803,7 @@
       </c>
       <c r="G241" s="3">
         <f t="shared" si="3"/>
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="H241" t="s">
         <v>799</v>
@@ -16849,7 +16858,13 @@
       </c>
       <c r="G242" s="3">
         <f t="shared" si="3"/>
-        <v>10.3</v>
+        <v>10</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I242" s="4" t="s">
+        <v>1050</v>
       </c>
       <c r="K242" t="s">
         <v>661</v>
@@ -16873,7 +16888,7 @@
         <v>698</v>
       </c>
       <c r="T242" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="243" spans="1:20" x14ac:dyDescent="0.2">
@@ -16898,7 +16913,13 @@
       </c>
       <c r="G243" s="3">
         <f t="shared" si="3"/>
-        <v>11.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="H243" t="s">
+        <v>310</v>
+      </c>
+      <c r="I243" s="4" t="s">
+        <v>1051</v>
       </c>
       <c r="K243" t="s">
         <v>661</v>
@@ -16922,7 +16943,7 @@
         <v>698</v>
       </c>
       <c r="T243" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="244" spans="1:20" x14ac:dyDescent="0.2">
@@ -16947,7 +16968,7 @@
       </c>
       <c r="G244" s="3">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="H244" t="s">
         <v>311</v>
@@ -17003,7 +17024,7 @@
       </c>
       <c r="G245" s="3">
         <f t="shared" si="3"/>
-        <v>-4.3</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>706</v>
@@ -17058,7 +17079,7 @@
       </c>
       <c r="G246" s="3">
         <f t="shared" si="3"/>
-        <v>16.7</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="H246" t="s">
         <v>313</v>
@@ -17114,7 +17135,7 @@
       </c>
       <c r="G247" s="3">
         <f t="shared" si="3"/>
-        <v>-21.8</v>
+        <v>-22.1</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>708</v>
@@ -17169,7 +17190,7 @@
       </c>
       <c r="G248" s="3">
         <f t="shared" si="3"/>
-        <v>10.1</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H248" t="s">
         <v>315</v>
@@ -17225,7 +17246,7 @@
       </c>
       <c r="G249" s="3">
         <f t="shared" si="3"/>
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="H249" s="6" t="s">
         <v>316</v>
@@ -17281,7 +17302,7 @@
       </c>
       <c r="G250" s="3">
         <f t="shared" si="3"/>
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>711</v>
@@ -17336,7 +17357,7 @@
       </c>
       <c r="G251" s="3">
         <f t="shared" si="3"/>
-        <v>32.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="H251" t="s">
         <v>318</v>
@@ -17388,7 +17409,7 @@
       </c>
       <c r="G252" s="3">
         <f t="shared" si="3"/>
-        <v>7.1999999999999993</v>
+        <v>6.9</v>
       </c>
       <c r="H252" t="s">
         <v>319</v>
@@ -17443,7 +17464,7 @@
       </c>
       <c r="G253" s="3">
         <f t="shared" si="3"/>
-        <v>59.099999999999994</v>
+        <v>58.8</v>
       </c>
       <c r="H253" t="s">
         <v>320</v>
@@ -17499,7 +17520,7 @@
       </c>
       <c r="G254" s="3">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="H254" t="s">
         <v>713</v>
@@ -17555,7 +17576,7 @@
       </c>
       <c r="G255" s="3">
         <f t="shared" si="3"/>
-        <v>32.200000000000003</v>
+        <v>31.9</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>715</v>
@@ -17611,7 +17632,7 @@
       </c>
       <c r="G256" s="3">
         <f t="shared" si="3"/>
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="H256" t="s">
         <v>323</v>
@@ -17666,7 +17687,7 @@
       </c>
       <c r="G257" s="3">
         <f t="shared" si="3"/>
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H257" t="s">
         <v>776</v>
@@ -17721,7 +17742,7 @@
       </c>
       <c r="G258" s="3">
         <f t="shared" si="3"/>
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="H258" t="s">
         <v>325</v>
@@ -17775,8 +17796,8 @@
         <v>-1.8000000000000043</v>
       </c>
       <c r="G259" s="3">
-        <f t="shared" ref="G259:G322" si="4">E259+6.8+1.5</f>
-        <v>-1.7999999999999998</v>
+        <f t="shared" ref="G259:G322" si="4">E259+6.5+1.5</f>
+        <v>-2.0999999999999996</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>831</v>
@@ -17831,7 +17852,7 @@
       </c>
       <c r="G260" s="3">
         <f t="shared" si="4"/>
-        <v>-5.6000000000000005</v>
+        <v>-5.9</v>
       </c>
       <c r="H260" s="4" t="s">
         <v>832</v>
@@ -17886,7 +17907,7 @@
       </c>
       <c r="G261" s="3">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H261" t="s">
         <v>328</v>
@@ -17941,7 +17962,7 @@
       </c>
       <c r="G262" s="3">
         <f t="shared" si="4"/>
-        <v>9.6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H262" t="s">
         <v>329</v>
@@ -17996,7 +18017,7 @@
       </c>
       <c r="G263" s="3">
         <f t="shared" si="4"/>
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="H263" t="s">
         <v>330</v>
@@ -18051,7 +18072,7 @@
       </c>
       <c r="G264" s="3">
         <f t="shared" si="4"/>
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="H264" t="s">
         <v>331</v>
@@ -18106,7 +18127,7 @@
       </c>
       <c r="G265" s="3">
         <f t="shared" si="4"/>
-        <v>54.199999999999996</v>
+        <v>53.9</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>837</v>
@@ -18161,7 +18182,7 @@
       </c>
       <c r="G266" s="3">
         <f t="shared" si="4"/>
-        <v>52.3</v>
+        <v>52</v>
       </c>
       <c r="H266" t="s">
         <v>333</v>
@@ -18216,7 +18237,7 @@
       </c>
       <c r="G267" s="3">
         <f t="shared" si="4"/>
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="H267" t="s">
         <v>334</v>
@@ -18271,7 +18292,7 @@
       </c>
       <c r="G268" s="3">
         <f t="shared" si="4"/>
-        <v>68.7</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="H268" s="4" t="s">
         <v>841</v>
@@ -18326,7 +18347,7 @@
       </c>
       <c r="G269" s="3">
         <f t="shared" si="4"/>
-        <v>-16.099999999999998</v>
+        <v>-16.399999999999999</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>843</v>
@@ -18381,7 +18402,7 @@
       </c>
       <c r="G270" s="3">
         <f t="shared" si="4"/>
-        <v>71.900000000000006</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="H270" s="4" t="s">
         <v>844</v>
@@ -18436,7 +18457,7 @@
       </c>
       <c r="G271" s="3">
         <f t="shared" si="4"/>
-        <v>67.599999999999994</v>
+        <v>67.3</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>846</v>
@@ -18491,7 +18512,7 @@
       </c>
       <c r="G272" s="3">
         <f t="shared" si="4"/>
-        <v>40.1</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="H272" s="6" t="s">
         <v>339</v>
@@ -18546,7 +18567,7 @@
       </c>
       <c r="G273" s="3">
         <f t="shared" si="4"/>
-        <v>56.599999999999994</v>
+        <v>56.3</v>
       </c>
       <c r="H273" s="6" t="s">
         <v>340</v>
@@ -18601,7 +18622,7 @@
       </c>
       <c r="G274" s="3">
         <f t="shared" si="4"/>
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="H274" s="6" t="s">
         <v>341</v>
@@ -18656,7 +18677,7 @@
       </c>
       <c r="G275" s="3">
         <f t="shared" si="4"/>
-        <v>8.8999999999999986</v>
+        <v>8.6</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>851</v>
@@ -18711,7 +18732,7 @@
       </c>
       <c r="G276" s="3">
         <f t="shared" si="4"/>
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="H276" s="6" t="s">
         <v>343</v>
@@ -18766,7 +18787,7 @@
       </c>
       <c r="G277" s="3">
         <f t="shared" si="4"/>
-        <v>10.1</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H277" s="6" t="s">
         <v>344</v>
@@ -18822,7 +18843,7 @@
       </c>
       <c r="G278" s="3">
         <f t="shared" si="4"/>
-        <v>22.500000000000004</v>
+        <v>22.200000000000003</v>
       </c>
       <c r="H278" s="6" t="s">
         <v>345</v>
@@ -18877,7 +18898,7 @@
       </c>
       <c r="G279" s="3">
         <f t="shared" si="4"/>
-        <v>-12.399999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>855</v>
@@ -18932,7 +18953,7 @@
       </c>
       <c r="G280" s="3">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="H280" s="6" t="s">
         <v>347</v>
@@ -18987,7 +19008,7 @@
       </c>
       <c r="G281" s="3">
         <f t="shared" si="4"/>
-        <v>-12.7</v>
+        <v>-13</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>858</v>
@@ -19042,7 +19063,7 @@
       </c>
       <c r="G282" s="3">
         <f t="shared" si="4"/>
-        <v>-14.8</v>
+        <v>-15.100000000000001</v>
       </c>
       <c r="H282" s="4" t="s">
         <v>859</v>
@@ -19097,7 +19118,7 @@
       </c>
       <c r="G283" s="3">
         <f t="shared" si="4"/>
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="H283" s="6" t="s">
         <v>860</v>
@@ -19152,7 +19173,7 @@
       </c>
       <c r="G284" s="3">
         <f t="shared" si="4"/>
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>351</v>
@@ -19207,7 +19228,7 @@
       </c>
       <c r="G285" s="3">
         <f t="shared" si="4"/>
-        <v>-3.3</v>
+        <v>-3.5999999999999996</v>
       </c>
       <c r="H285" t="s">
         <v>352</v>
@@ -19263,7 +19284,7 @@
       </c>
       <c r="G286" s="3">
         <f t="shared" si="4"/>
-        <v>42.599999999999994</v>
+        <v>42.3</v>
       </c>
       <c r="H286" t="s">
         <v>354</v>
@@ -19319,7 +19340,7 @@
       </c>
       <c r="G287" s="3">
         <f t="shared" si="4"/>
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>357</v>
@@ -19374,7 +19395,7 @@
       </c>
       <c r="G288" s="3">
         <f t="shared" si="4"/>
-        <v>53.599999999999994</v>
+        <v>53.3</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>358</v>
@@ -19430,7 +19451,7 @@
       </c>
       <c r="G289" s="3">
         <f t="shared" si="4"/>
-        <v>-9.5</v>
+        <v>-9.8000000000000007</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>361</v>
@@ -19485,7 +19506,7 @@
       </c>
       <c r="G290" s="3">
         <f t="shared" si="4"/>
-        <v>-8.6999999999999993</v>
+        <v>-9</v>
       </c>
       <c r="H290" s="4" t="s">
         <v>363</v>
@@ -19540,7 +19561,7 @@
       </c>
       <c r="G291" s="3">
         <f t="shared" si="4"/>
-        <v>-5.5000000000000009</v>
+        <v>-5.8000000000000007</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>365</v>
@@ -19595,7 +19616,7 @@
       </c>
       <c r="G292" s="3">
         <f t="shared" si="4"/>
-        <v>-11.3</v>
+        <v>-11.600000000000001</v>
       </c>
       <c r="H292" s="4" t="s">
         <v>368</v>
@@ -19650,7 +19671,7 @@
       </c>
       <c r="G293" s="3">
         <f t="shared" si="4"/>
-        <v>-7.5</v>
+        <v>-7.8000000000000007</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>370</v>
@@ -19705,7 +19726,7 @@
       </c>
       <c r="G294" s="3">
         <f t="shared" si="4"/>
-        <v>-9.3999999999999986</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="H294" s="4" t="s">
         <v>372</v>
@@ -19760,7 +19781,7 @@
       </c>
       <c r="G295" s="3">
         <f t="shared" si="4"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.5</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>374</v>
@@ -19815,7 +19836,7 @@
       </c>
       <c r="G296" s="3">
         <f t="shared" si="4"/>
-        <v>54.5</v>
+        <v>54.2</v>
       </c>
       <c r="H296" s="6" t="s">
         <v>375</v>
@@ -19871,7 +19892,7 @@
       </c>
       <c r="G297" s="3">
         <f t="shared" si="4"/>
-        <v>-8.5</v>
+        <v>-8.8000000000000007</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>378</v>
@@ -19926,7 +19947,7 @@
       </c>
       <c r="G298" s="3">
         <f t="shared" si="4"/>
-        <v>-6.8000000000000007</v>
+        <v>-7.1</v>
       </c>
       <c r="H298" s="4" t="s">
         <v>380</v>
@@ -19981,7 +20002,7 @@
       </c>
       <c r="G299" s="3">
         <f t="shared" si="4"/>
-        <v>-28.499999999999996</v>
+        <v>-28.799999999999997</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>895</v>
@@ -20036,7 +20057,7 @@
       </c>
       <c r="G300" s="3">
         <f t="shared" si="4"/>
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H300" s="6" t="s">
         <v>382</v>
@@ -20092,7 +20113,7 @@
       </c>
       <c r="G301" s="3">
         <f t="shared" si="4"/>
-        <v>-33.800000000000004</v>
+        <v>-34.1</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>385</v>
@@ -20148,7 +20169,7 @@
       </c>
       <c r="G302" s="3">
         <f t="shared" si="4"/>
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="H302" t="s">
         <v>386</v>
@@ -20204,7 +20225,7 @@
       </c>
       <c r="G303" s="3">
         <f t="shared" si="4"/>
-        <v>-34.300000000000004</v>
+        <v>-34.6</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>389</v>
@@ -20260,7 +20281,7 @@
       </c>
       <c r="G304" s="3">
         <f t="shared" si="4"/>
-        <v>-15.399999999999999</v>
+        <v>-15.7</v>
       </c>
       <c r="H304" s="4" t="s">
         <v>391</v>
@@ -20316,7 +20337,7 @@
       </c>
       <c r="G305" s="3">
         <f t="shared" si="4"/>
-        <v>-26.3</v>
+        <v>-26.6</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>393</v>
@@ -20372,7 +20393,7 @@
       </c>
       <c r="G306" s="3">
         <f t="shared" si="4"/>
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="H306" s="4" t="s">
         <v>395</v>
@@ -20428,7 +20449,7 @@
       </c>
       <c r="G307" s="3">
         <f t="shared" si="4"/>
-        <v>-7.3000000000000007</v>
+        <v>-7.6</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>397</v>
@@ -20484,7 +20505,7 @@
       </c>
       <c r="G308" s="3">
         <f t="shared" si="4"/>
-        <v>-2.2000000000000002</v>
+        <v>-2.5</v>
       </c>
       <c r="H308" t="s">
         <v>398</v>
@@ -20540,7 +20561,7 @@
       </c>
       <c r="G309" s="3">
         <f t="shared" si="4"/>
-        <v>0.59999999999999964</v>
+        <v>0.29999999999999982</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>401</v>
@@ -20596,7 +20617,7 @@
       </c>
       <c r="G310" s="3">
         <f t="shared" si="4"/>
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="H310" t="s">
         <v>402</v>
@@ -20652,7 +20673,7 @@
       </c>
       <c r="G311" s="3">
         <f t="shared" si="4"/>
-        <v>-21.7</v>
+        <v>-22</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>405</v>
@@ -20707,7 +20728,7 @@
       </c>
       <c r="G312" s="3">
         <f t="shared" si="4"/>
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H312" t="s">
         <v>406</v>
@@ -20763,7 +20784,7 @@
       </c>
       <c r="G313" s="3">
         <f t="shared" si="4"/>
-        <v>-12</v>
+        <v>-12.3</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>409</v>
@@ -20818,7 +20839,7 @@
       </c>
       <c r="G314" s="3">
         <f t="shared" si="4"/>
-        <v>-1.7000000000000002</v>
+        <v>-2</v>
       </c>
       <c r="H314" s="4" t="s">
         <v>411</v>
@@ -20873,7 +20894,7 @@
       </c>
       <c r="G315" s="3">
         <f t="shared" si="4"/>
-        <v>-13.2</v>
+        <v>-13.5</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>1035</v>
@@ -20928,7 +20949,7 @@
       </c>
       <c r="G316" s="3">
         <f t="shared" si="4"/>
-        <v>-47.300000000000004</v>
+        <v>-47.6</v>
       </c>
       <c r="H316" s="4" t="s">
         <v>1036</v>
@@ -20983,7 +21004,7 @@
       </c>
       <c r="G317" s="3">
         <f t="shared" si="4"/>
-        <v>-36.5</v>
+        <v>-36.799999999999997</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>1037</v>
@@ -21038,7 +21059,7 @@
       </c>
       <c r="G318" s="3">
         <f t="shared" si="4"/>
-        <v>-24.599999999999998</v>
+        <v>-24.9</v>
       </c>
       <c r="H318" s="4" t="s">
         <v>1038</v>
@@ -21093,7 +21114,7 @@
       </c>
       <c r="G319" s="3">
         <f t="shared" si="4"/>
-        <v>-9.8999999999999986</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>1039</v>
@@ -21148,7 +21169,7 @@
       </c>
       <c r="G320" s="3">
         <f t="shared" si="4"/>
-        <v>45.9</v>
+        <v>45.6</v>
       </c>
       <c r="H320" s="6" t="s">
         <v>417</v>
@@ -21204,7 +21225,7 @@
       </c>
       <c r="G321" s="3">
         <f t="shared" si="4"/>
-        <v>-18.8</v>
+        <v>-19.100000000000001</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>420</v>
@@ -21260,7 +21281,7 @@
       </c>
       <c r="G322" s="3">
         <f t="shared" si="4"/>
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="H322" s="6" t="s">
         <v>421</v>
@@ -21315,8 +21336,8 @@
         <v>12.700000000000003</v>
       </c>
       <c r="G323" s="3">
-        <f t="shared" ref="G323:G386" si="5">E323+6.8+1.5</f>
-        <v>20.3</v>
+        <f t="shared" ref="G323:G386" si="5">E323+6.5+1.5</f>
+        <v>20</v>
       </c>
       <c r="H323" s="6" t="s">
         <v>423</v>
@@ -21372,7 +21393,7 @@
       </c>
       <c r="G324" s="3">
         <f t="shared" si="5"/>
-        <v>16.899999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="H324" s="6" t="s">
         <v>425</v>
@@ -21428,7 +21449,7 @@
       </c>
       <c r="G325" s="3">
         <f t="shared" si="5"/>
-        <v>19.600000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="H325" s="6" t="s">
         <v>427</v>
@@ -21484,7 +21505,7 @@
       </c>
       <c r="G326" s="3">
         <f t="shared" si="5"/>
-        <v>8.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H326" s="4" t="s">
         <v>430</v>
@@ -21539,7 +21560,7 @@
       </c>
       <c r="G327" s="3">
         <f t="shared" si="5"/>
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="H327" t="s">
         <v>431</v>
@@ -21595,7 +21616,7 @@
       </c>
       <c r="G328" s="3">
         <f t="shared" si="5"/>
-        <v>85.6</v>
+        <v>85.3</v>
       </c>
       <c r="H328" s="6" t="s">
         <v>434</v>
@@ -21648,7 +21669,7 @@
       </c>
       <c r="G329" s="3">
         <f t="shared" si="5"/>
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="H329" t="s">
         <v>435</v>
@@ -21704,7 +21725,7 @@
       </c>
       <c r="G330" s="3">
         <f t="shared" si="5"/>
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="H330" s="6" t="s">
         <v>437</v>
@@ -21760,7 +21781,7 @@
       </c>
       <c r="G331" s="3">
         <f t="shared" si="5"/>
-        <v>19.7</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="H331" t="s">
         <v>439</v>
@@ -21816,7 +21837,7 @@
       </c>
       <c r="G332" s="3">
         <f t="shared" si="5"/>
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="H332" s="4" t="s">
         <v>442</v>
@@ -21872,7 +21893,7 @@
       </c>
       <c r="G333" s="3">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000018</v>
+        <v>-0.5</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>444</v>
@@ -21928,7 +21949,7 @@
       </c>
       <c r="G334" s="3">
         <f t="shared" si="5"/>
-        <v>-29.599999999999998</v>
+        <v>-29.9</v>
       </c>
       <c r="H334" s="4" t="s">
         <v>446</v>
@@ -21984,7 +22005,7 @@
       </c>
       <c r="G335" s="3">
         <f t="shared" si="5"/>
-        <v>3.0999999999999996</v>
+        <v>2.8</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>448</v>
@@ -22040,7 +22061,7 @@
       </c>
       <c r="G336" s="3">
         <f t="shared" si="5"/>
-        <v>-13.099999999999998</v>
+        <v>-13.399999999999999</v>
       </c>
       <c r="H336" s="4" t="s">
         <v>450</v>
@@ -22096,7 +22117,7 @@
       </c>
       <c r="G337" s="3">
         <f t="shared" si="5"/>
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="H337" s="6" t="s">
         <v>451</v>
@@ -22152,7 +22173,7 @@
       </c>
       <c r="G338" s="3">
         <f t="shared" si="5"/>
-        <v>-37.200000000000003</v>
+        <v>-37.5</v>
       </c>
       <c r="H338" s="4" t="s">
         <v>454</v>
@@ -22208,7 +22229,7 @@
       </c>
       <c r="G339" s="3">
         <f t="shared" si="5"/>
-        <v>-25.099999999999998</v>
+        <v>-25.4</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>456</v>
@@ -22264,7 +22285,7 @@
       </c>
       <c r="G340" s="3">
         <f t="shared" si="5"/>
-        <v>-29.7</v>
+        <v>-30</v>
       </c>
       <c r="H340" s="4" t="s">
         <v>458</v>
@@ -22320,7 +22341,7 @@
       </c>
       <c r="G341" s="3">
         <f t="shared" si="5"/>
-        <v>-14.5</v>
+        <v>-14.8</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>460</v>
@@ -22376,7 +22397,7 @@
       </c>
       <c r="G342" s="3">
         <f t="shared" si="5"/>
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H342" t="s">
         <v>461</v>
@@ -22432,7 +22453,7 @@
       </c>
       <c r="G343" s="3">
         <f t="shared" si="5"/>
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="K343" t="s">
         <v>661</v>
@@ -22481,7 +22502,7 @@
       </c>
       <c r="G344" s="3">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="K344" t="s">
         <v>661</v>
@@ -22530,7 +22551,7 @@
       </c>
       <c r="G345" s="3">
         <f t="shared" si="5"/>
-        <v>-4.8</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>872</v>
@@ -22585,7 +22606,7 @@
       </c>
       <c r="G346" s="3">
         <f t="shared" si="5"/>
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="H346" s="4" t="s">
         <v>874</v>
@@ -22640,7 +22661,7 @@
       </c>
       <c r="G347" s="3">
         <f t="shared" si="5"/>
-        <v>-34.700000000000003</v>
+        <v>-35</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>798</v>
@@ -22695,7 +22716,7 @@
       </c>
       <c r="G348" s="3">
         <f t="shared" si="5"/>
-        <v>-15.3</v>
+        <v>-15.600000000000001</v>
       </c>
       <c r="H348" s="4" t="s">
         <v>785</v>
@@ -22750,7 +22771,7 @@
       </c>
       <c r="G349" s="3">
         <f t="shared" si="5"/>
-        <v>-14.5</v>
+        <v>-14.8</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>797</v>
@@ -22805,7 +22826,7 @@
       </c>
       <c r="G350" s="3">
         <f t="shared" si="5"/>
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="H350" t="s">
         <v>783</v>
@@ -22860,7 +22881,7 @@
       </c>
       <c r="G351" s="3">
         <f t="shared" si="5"/>
-        <v>-18.099999999999998</v>
+        <v>-18.399999999999999</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>787</v>
@@ -22915,7 +22936,7 @@
       </c>
       <c r="G352" s="3">
         <f t="shared" si="5"/>
-        <v>-20.9</v>
+        <v>-21.2</v>
       </c>
       <c r="H352" s="4" t="s">
         <v>724</v>
@@ -22972,7 +22993,7 @@
       </c>
       <c r="G353" s="3">
         <f t="shared" si="5"/>
-        <v>-49.500000000000007</v>
+        <v>-49.800000000000004</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>946</v>
@@ -23028,7 +23049,7 @@
       </c>
       <c r="G354" s="3">
         <f t="shared" si="5"/>
-        <v>-25.500000000000004</v>
+        <v>-25.800000000000004</v>
       </c>
       <c r="H354" s="4" t="s">
         <v>947</v>
@@ -23084,7 +23105,7 @@
       </c>
       <c r="G355" s="3">
         <f t="shared" si="5"/>
-        <v>-27.400000000000002</v>
+        <v>-27.700000000000003</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>948</v>
@@ -23140,7 +23161,7 @@
       </c>
       <c r="G356" s="3">
         <f t="shared" si="5"/>
-        <v>-15.600000000000005</v>
+        <v>-15.900000000000006</v>
       </c>
       <c r="H356" s="4" t="s">
         <v>954</v>
@@ -23196,7 +23217,7 @@
       </c>
       <c r="G357" s="3">
         <f t="shared" si="5"/>
-        <v>-14.8</v>
+        <v>-15.100000000000001</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>957</v>
@@ -23252,7 +23273,7 @@
       </c>
       <c r="G358" s="3">
         <f t="shared" si="5"/>
-        <v>-18.2</v>
+        <v>-18.5</v>
       </c>
       <c r="H358" s="4" t="s">
         <v>955</v>
@@ -23308,7 +23329,7 @@
       </c>
       <c r="G359" s="3">
         <f t="shared" si="5"/>
-        <v>-14.099999999999998</v>
+        <v>-14.399999999999999</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>953</v>
@@ -23364,7 +23385,7 @@
       </c>
       <c r="G360" s="3">
         <f t="shared" si="5"/>
-        <v>-11.899999999999995</v>
+        <v>-12.199999999999996</v>
       </c>
       <c r="H360" s="4" t="s">
         <v>951</v>
@@ -23420,7 +23441,7 @@
       </c>
       <c r="G361" s="3">
         <f t="shared" si="5"/>
-        <v>-12.8</v>
+        <v>-13.100000000000001</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>949</v>
@@ -23475,7 +23496,7 @@
       </c>
       <c r="G362" s="3">
         <f t="shared" si="5"/>
-        <v>-41.1</v>
+        <v>-41.4</v>
       </c>
       <c r="H362" s="4" t="s">
         <v>483</v>
@@ -23530,7 +23551,7 @@
       </c>
       <c r="G363" s="3">
         <f t="shared" si="5"/>
-        <v>-14.5</v>
+        <v>-14.8</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>485</v>
@@ -23586,7 +23607,7 @@
       </c>
       <c r="G364" s="3">
         <f t="shared" si="5"/>
-        <v>-15</v>
+        <v>-15.3</v>
       </c>
       <c r="H364" s="4" t="s">
         <v>488</v>
@@ -23641,7 +23662,7 @@
       </c>
       <c r="G365" s="3">
         <f t="shared" si="5"/>
-        <v>-16.3</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>490</v>
@@ -23696,7 +23717,7 @@
       </c>
       <c r="G366" s="3">
         <f t="shared" si="5"/>
-        <v>-13.2</v>
+        <v>-13.5</v>
       </c>
       <c r="H366" s="4" t="s">
         <v>492</v>
@@ -23751,7 +23772,7 @@
       </c>
       <c r="G367" s="3">
         <f t="shared" si="5"/>
-        <v>-14.5</v>
+        <v>-14.8</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>494</v>
@@ -23806,7 +23827,7 @@
       </c>
       <c r="G368" s="3">
         <f t="shared" si="5"/>
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="H368" t="s">
         <v>495</v>
@@ -23862,7 +23883,7 @@
       </c>
       <c r="G369" s="3">
         <f t="shared" si="5"/>
-        <v>-19.3</v>
+        <v>-19.600000000000001</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>498</v>
@@ -23918,7 +23939,7 @@
       </c>
       <c r="G370" s="3">
         <f t="shared" si="5"/>
-        <v>-11.5</v>
+        <v>-11.8</v>
       </c>
       <c r="H370" s="4" t="s">
         <v>500</v>
@@ -23974,7 +23995,7 @@
       </c>
       <c r="G371" s="3">
         <f t="shared" si="5"/>
-        <v>-14.2</v>
+        <v>-14.5</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>503</v>
@@ -24030,7 +24051,7 @@
       </c>
       <c r="G372" s="3">
         <f t="shared" si="5"/>
-        <v>-25.999999999999996</v>
+        <v>-26.299999999999997</v>
       </c>
       <c r="H372" s="4" t="s">
         <v>506</v>
@@ -24085,7 +24106,7 @@
       </c>
       <c r="G373" s="3">
         <f t="shared" si="5"/>
-        <v>-15.5</v>
+        <v>-15.8</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>508</v>
@@ -24140,7 +24161,7 @@
       </c>
       <c r="G374" s="3">
         <f t="shared" si="5"/>
-        <v>-37.800000000000004</v>
+        <v>-38.1</v>
       </c>
       <c r="H374" s="4" t="s">
         <v>510</v>
@@ -24195,7 +24216,7 @@
       </c>
       <c r="G375" s="3">
         <f t="shared" si="5"/>
-        <v>-15.899999999999999</v>
+        <v>-16.2</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>810</v>
@@ -24250,7 +24271,7 @@
       </c>
       <c r="G376" s="3">
         <f t="shared" si="5"/>
-        <v>-9.5</v>
+        <v>-9.8000000000000007</v>
       </c>
       <c r="H376" s="4" t="s">
         <v>513</v>
@@ -24305,7 +24326,7 @@
       </c>
       <c r="G377" s="3">
         <f t="shared" si="5"/>
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="H377" t="s">
         <v>514</v>
@@ -24362,7 +24383,7 @@
       </c>
       <c r="G378" s="3">
         <f t="shared" si="5"/>
-        <v>-9.6999999999999993</v>
+        <v>-10</v>
       </c>
       <c r="H378" s="4" t="s">
         <v>517</v>
@@ -24417,7 +24438,7 @@
       </c>
       <c r="G379" s="3">
         <f t="shared" si="5"/>
-        <v>63.099999999999994</v>
+        <v>62.8</v>
       </c>
       <c r="H379" t="s">
         <v>519</v>
@@ -24473,7 +24494,7 @@
       </c>
       <c r="G380" s="3">
         <f t="shared" si="5"/>
-        <v>-43.300000000000004</v>
+        <v>-43.6</v>
       </c>
       <c r="H380" s="4" t="s">
         <v>522</v>
@@ -24529,7 +24550,7 @@
       </c>
       <c r="G381" s="3">
         <f t="shared" si="5"/>
-        <v>36.699999999999996</v>
+        <v>36.4</v>
       </c>
       <c r="H381" t="s">
         <v>524</v>
@@ -24585,7 +24606,7 @@
       </c>
       <c r="G382" s="3">
         <f t="shared" si="5"/>
-        <v>-13.5</v>
+        <v>-13.8</v>
       </c>
       <c r="H382" s="4" t="s">
         <v>527</v>
@@ -24641,7 +24662,7 @@
       </c>
       <c r="G383" s="3">
         <f t="shared" si="5"/>
-        <v>-13.8</v>
+        <v>-14.100000000000001</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>530</v>
@@ -24697,7 +24718,7 @@
       </c>
       <c r="G384" s="3">
         <f t="shared" si="5"/>
-        <v>-6.3999999999999995</v>
+        <v>-6.6999999999999993</v>
       </c>
       <c r="H384" s="4" t="s">
         <v>533</v>
@@ -24753,7 +24774,7 @@
       </c>
       <c r="G385" s="3">
         <f t="shared" si="5"/>
-        <v>-7.6999999999999993</v>
+        <v>-8</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>536</v>
@@ -24808,7 +24829,7 @@
       </c>
       <c r="G386" s="3">
         <f t="shared" si="5"/>
-        <v>-15.7</v>
+        <v>-16</v>
       </c>
       <c r="H386" s="4" t="s">
         <v>538</v>
@@ -24862,8 +24883,8 @@
         <v>-18.5</v>
       </c>
       <c r="G387" s="3">
-        <f t="shared" ref="G387:G436" si="6">E387+6.8+1.5</f>
-        <v>-15.399999999999999</v>
+        <f t="shared" ref="G387:G436" si="6">E387+6.5+1.5</f>
+        <v>-15.7</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>540</v>
@@ -24918,7 +24939,7 @@
       </c>
       <c r="G388" s="3">
         <f t="shared" si="6"/>
-        <v>-12.8</v>
+        <v>-13.100000000000001</v>
       </c>
       <c r="H388" s="4" t="s">
         <v>542</v>
@@ -24973,7 +24994,7 @@
       </c>
       <c r="G389" s="3">
         <f t="shared" si="6"/>
-        <v>-2.0000000000000009</v>
+        <v>-2.3000000000000007</v>
       </c>
       <c r="H389" t="s">
         <v>543</v>
@@ -25029,7 +25050,7 @@
       </c>
       <c r="G390" s="3">
         <f t="shared" si="6"/>
-        <v>38.699999999999996</v>
+        <v>38.4</v>
       </c>
       <c r="H390" s="6" t="s">
         <v>545</v>
@@ -25085,7 +25106,7 @@
       </c>
       <c r="G391" s="3">
         <f t="shared" si="6"/>
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>548</v>
@@ -25141,7 +25162,7 @@
       </c>
       <c r="G392" s="3">
         <f t="shared" si="6"/>
-        <v>-13.5</v>
+        <v>-13.8</v>
       </c>
       <c r="H392" s="4" t="s">
         <v>551</v>
@@ -25196,7 +25217,7 @@
       </c>
       <c r="G393" s="3">
         <f t="shared" si="6"/>
-        <v>-9.3999999999999986</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>552</v>
@@ -25252,7 +25273,7 @@
       </c>
       <c r="G394" s="3">
         <f t="shared" si="6"/>
-        <v>40.799999999999997</v>
+        <v>40.5</v>
       </c>
       <c r="H394" s="4" t="s">
         <v>555</v>
@@ -25308,7 +25329,7 @@
       </c>
       <c r="G395" s="3">
         <f t="shared" si="6"/>
-        <v>-1.7999999999999998</v>
+        <v>-2.0999999999999996</v>
       </c>
       <c r="H395" t="s">
         <v>557</v>
@@ -25364,7 +25385,7 @@
       </c>
       <c r="G396" s="3">
         <f t="shared" si="6"/>
-        <v>-2.1000000000000005</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="H396" s="4" t="s">
         <v>559</v>
@@ -25420,7 +25441,7 @@
       </c>
       <c r="G397" s="3">
         <f t="shared" si="6"/>
-        <v>-16.599999999999998</v>
+        <v>-16.899999999999999</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>562</v>
@@ -25475,7 +25496,7 @@
       </c>
       <c r="G398" s="3">
         <f t="shared" si="6"/>
-        <v>64.5</v>
+        <v>64.2</v>
       </c>
       <c r="H398" t="s">
         <v>563</v>
@@ -25531,7 +25552,7 @@
       </c>
       <c r="G399" s="3">
         <f t="shared" si="6"/>
-        <v>-12.599999999999998</v>
+        <v>-12.899999999999999</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>566</v>
@@ -25587,7 +25608,7 @@
       </c>
       <c r="G400" s="3">
         <f t="shared" si="6"/>
-        <v>31.900000000000002</v>
+        <v>31.6</v>
       </c>
       <c r="H400" s="4" t="s">
         <v>875</v>
@@ -25642,7 +25663,7 @@
       </c>
       <c r="G401" s="3">
         <f t="shared" si="6"/>
-        <v>-20.599999999999998</v>
+        <v>-20.9</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>877</v>
@@ -25697,7 +25718,7 @@
       </c>
       <c r="G402" s="3">
         <f t="shared" si="6"/>
-        <v>-33</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="H402" s="4" t="s">
         <v>878</v>
@@ -25752,7 +25773,7 @@
       </c>
       <c r="G403" s="3">
         <f t="shared" si="6"/>
-        <v>-24.099999999999998</v>
+        <v>-24.4</v>
       </c>
       <c r="H403" s="4" t="s">
         <v>879</v>
@@ -25807,7 +25828,7 @@
       </c>
       <c r="G404" s="3">
         <f t="shared" si="6"/>
-        <v>43.099999999999994</v>
+        <v>42.8</v>
       </c>
       <c r="H404" s="4" t="s">
         <v>572</v>
@@ -25863,7 +25884,7 @@
       </c>
       <c r="G405" s="3">
         <f t="shared" si="6"/>
-        <v>3.4000000000000012</v>
+        <v>3.1000000000000014</v>
       </c>
       <c r="H405" s="4" t="s">
         <v>905</v>
@@ -25919,7 +25940,7 @@
       </c>
       <c r="G406" s="3">
         <f t="shared" si="6"/>
-        <v>8.100000000000005</v>
+        <v>7.8000000000000043</v>
       </c>
       <c r="H406" s="4" t="s">
         <v>902</v>
@@ -25975,7 +25996,7 @@
       </c>
       <c r="G407" s="3">
         <f t="shared" si="6"/>
-        <v>42.900000000000006</v>
+        <v>42.600000000000009</v>
       </c>
       <c r="H407" t="s">
         <v>575</v>
@@ -26031,7 +26052,7 @@
       </c>
       <c r="G408" s="3">
         <f t="shared" si="6"/>
-        <v>40.900000000000006</v>
+        <v>40.600000000000009</v>
       </c>
       <c r="H408" t="s">
         <v>576</v>
@@ -26087,7 +26108,7 @@
       </c>
       <c r="G409" s="3">
         <f t="shared" si="6"/>
-        <v>-3.8999999999999959</v>
+        <v>-4.1999999999999957</v>
       </c>
       <c r="H409" s="4" t="s">
         <v>904</v>
@@ -26143,7 +26164,7 @@
       </c>
       <c r="G410" s="3">
         <f t="shared" si="6"/>
-        <v>-15.7</v>
+        <v>-16</v>
       </c>
       <c r="H410" s="4" t="s">
         <v>898</v>
@@ -26199,7 +26220,7 @@
       </c>
       <c r="G411" s="3">
         <f t="shared" si="6"/>
-        <v>11.2</v>
+        <v>10.899999999999999</v>
       </c>
       <c r="H411" t="s">
         <v>579</v>
@@ -26255,7 +26276,7 @@
       </c>
       <c r="G412" s="3">
         <f t="shared" si="6"/>
-        <v>57.5</v>
+        <v>57.2</v>
       </c>
       <c r="H412" t="s">
         <v>580</v>
@@ -26311,7 +26332,7 @@
       </c>
       <c r="G413" s="3">
         <f t="shared" si="6"/>
-        <v>-35.600000000000009</v>
+        <v>-35.900000000000006</v>
       </c>
       <c r="H413" s="4" t="s">
         <v>906</v>
@@ -26367,7 +26388,7 @@
       </c>
       <c r="G414" s="3">
         <f t="shared" si="6"/>
-        <v>16.600000000000005</v>
+        <v>16.300000000000004</v>
       </c>
       <c r="H414" t="s">
         <v>582</v>
@@ -26423,7 +26444,7 @@
       </c>
       <c r="G415" s="3">
         <f t="shared" si="6"/>
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="H415" t="s">
         <v>583</v>
@@ -26478,7 +26499,7 @@
       </c>
       <c r="G416" s="3">
         <f t="shared" si="6"/>
-        <v>36.799999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="H416" t="s">
         <v>584</v>
@@ -26533,7 +26554,7 @@
       </c>
       <c r="G417" s="3">
         <f t="shared" si="6"/>
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="H417" t="s">
         <v>585</v>
@@ -26588,7 +26609,7 @@
       </c>
       <c r="G418" s="3">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H418" t="s">
         <v>586</v>
@@ -26643,7 +26664,7 @@
       </c>
       <c r="G419" s="3">
         <f t="shared" si="6"/>
-        <v>-12.3</v>
+        <v>-12.600000000000001</v>
       </c>
       <c r="H419" s="4" t="s">
         <v>931</v>
@@ -26698,7 +26719,7 @@
       </c>
       <c r="G420" s="3">
         <f t="shared" si="6"/>
-        <v>-2.3999999999999995</v>
+        <v>-2.6999999999999993</v>
       </c>
       <c r="H420" s="4" t="s">
         <v>962</v>
@@ -26753,7 +26774,7 @@
       </c>
       <c r="G421" s="3">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="H421" t="s">
         <v>589</v>
@@ -26808,7 +26829,7 @@
       </c>
       <c r="G422" s="3">
         <f t="shared" si="6"/>
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="H422" t="s">
         <v>590</v>
@@ -26863,7 +26884,7 @@
       </c>
       <c r="G423" s="3">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H423" t="s">
         <v>591</v>
@@ -26918,7 +26939,7 @@
       </c>
       <c r="G424" s="3">
         <f t="shared" si="6"/>
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="H424" t="s">
         <v>592</v>
@@ -26973,7 +26994,7 @@
       </c>
       <c r="G425" s="3">
         <f t="shared" si="6"/>
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="H425" t="s">
         <v>593</v>
@@ -27028,7 +27049,7 @@
       </c>
       <c r="G426" s="3">
         <f t="shared" si="6"/>
-        <v>-36.1</v>
+        <v>-36.4</v>
       </c>
       <c r="H426" s="4" t="s">
         <v>595</v>
@@ -27083,7 +27104,7 @@
       </c>
       <c r="G427" s="3">
         <f t="shared" si="6"/>
-        <v>-31.300000000000004</v>
+        <v>-31.6</v>
       </c>
       <c r="H427" s="4" t="s">
         <v>597</v>
@@ -27138,7 +27159,7 @@
       </c>
       <c r="G428" s="3">
         <f t="shared" si="6"/>
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H428" s="4" t="s">
         <v>974</v>
@@ -27193,7 +27214,7 @@
       </c>
       <c r="G429" s="3">
         <f t="shared" si="6"/>
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="H429" t="s">
         <v>600</v>
@@ -27245,7 +27266,7 @@
       </c>
       <c r="G430" s="3">
         <f t="shared" si="6"/>
-        <v>0.89999999999999947</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="H430" s="4" t="s">
         <v>978</v>
@@ -27300,7 +27321,7 @@
       </c>
       <c r="G431" s="3">
         <f t="shared" si="6"/>
-        <v>59.699999999999996</v>
+        <v>59.4</v>
       </c>
       <c r="H431" t="s">
         <v>602</v>
@@ -27355,7 +27376,7 @@
       </c>
       <c r="G432" s="3">
         <f t="shared" si="6"/>
-        <v>-13.8</v>
+        <v>-14.100000000000001</v>
       </c>
       <c r="H432" s="4" t="s">
         <v>988</v>
@@ -27410,7 +27431,7 @@
       </c>
       <c r="G433" s="3">
         <f t="shared" si="6"/>
-        <v>-8.0999999999999979</v>
+        <v>-8.3999999999999986</v>
       </c>
       <c r="H433" s="4" t="s">
         <v>1040</v>
@@ -27465,7 +27486,7 @@
       </c>
       <c r="G434" s="3">
         <f t="shared" si="6"/>
-        <v>-14.2</v>
+        <v>-14.5</v>
       </c>
       <c r="H434" s="4" t="s">
         <v>991</v>
@@ -27520,7 +27541,7 @@
       </c>
       <c r="G435" s="3">
         <f t="shared" si="6"/>
-        <v>-7.8999999999999986</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="H435" s="4" t="s">
         <v>992</v>
@@ -27575,7 +27596,7 @@
       </c>
       <c r="G436" s="3">
         <f t="shared" si="6"/>
-        <v>-37.900000000000006</v>
+        <v>-38.200000000000003</v>
       </c>
       <c r="H436" s="4" t="s">
         <v>1028</v>

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA38ED3-0D0B-BE42-B9B2-CBE2869BB876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7147150E-71CB-6C49-99F3-B73E9DDCCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5619" uniqueCount="1055">
   <si>
     <t>State</t>
   </si>
@@ -3232,6 +3232,12 @@
   </si>
   <si>
     <t>Shaheen, Stefany</t>
+  </si>
+  <si>
+    <t>Keenan, Kellie</t>
+  </si>
+  <si>
+    <t>Mellor, Victor</t>
   </si>
 </sst>
 </file>
@@ -22455,6 +22461,12 @@
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
+      <c r="H343" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>1053</v>
+      </c>
       <c r="K343" t="s">
         <v>661</v>
       </c>
@@ -22477,7 +22489,7 @@
         <v>698</v>
       </c>
       <c r="T343" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="344" spans="1:20" x14ac:dyDescent="0.2">
@@ -22504,6 +22516,12 @@
         <f t="shared" si="5"/>
         <v>14.7</v>
       </c>
+      <c r="H344" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>1054</v>
+      </c>
       <c r="K344" t="s">
         <v>661</v>
       </c>
@@ -22526,7 +22544,7 @@
         <v>698</v>
       </c>
       <c r="T344" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="345" spans="1:20" x14ac:dyDescent="0.2">

--- a/inputs/House Model Data.xlsx
+++ b/inputs/House Model Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benyelin/Developer/house_model_python/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7147150E-71CB-6C49-99F3-B73E9DDCCAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E8CFE9-6D8E-2045-BEB8-3AD6A83BCE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1560" windowWidth="27640" windowHeight="16940" xr2:uid="{9CA4CF23-00BE-4A4E-B0A3-B27FE202FE9A}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5619" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5621" uniqueCount="1056">
   <si>
     <t>State</t>
   </si>
@@ -3238,6 +3238,9 @@
   </si>
   <si>
     <t>Mellor, Victor</t>
+  </si>
+  <si>
+    <t>Arminio, Joseph</t>
   </si>
 </sst>
 </file>
@@ -8439,6 +8442,12 @@
         <f t="shared" si="1"/>
         <v>22.7</v>
       </c>
+      <c r="H88" t="s">
+        <v>98</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>1055</v>
+      </c>
       <c r="K88" t="s">
         <v>674</v>
       </c>
